--- a/data/trans_orig/IP07A05-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A05-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse satisfecho con su vida en 2007 (tasa de respuesta: 99,7%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el adulto en 2007 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39015</t>
+          <t>39811</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56671</t>
+          <t>57042</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48164</t>
+          <t>49161</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66988</t>
+          <t>66984</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>91061</t>
+          <t>92481</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>117888</t>
+          <t>117428</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>43,64%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59707</t>
+          <t>59364</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77825</t>
+          <t>77730</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60925</t>
+          <t>62051</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80267</t>
+          <t>80467</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>126013</t>
+          <t>127518</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>153555</t>
+          <t>152870</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>56,82%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>4125</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12884</t>
+          <t>13091</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6148</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16632</t>
+          <t>17001</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12276</t>
+          <t>12528</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>26055</t>
+          <t>25811</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6034</t>
+          <t>5310</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>551</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7688</t>
+          <t>8342</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>3386</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3394</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>66922</t>
+          <t>67229</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88495</t>
+          <t>89512</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>71627</t>
+          <t>71610</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>93098</t>
+          <t>93632</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>147304</t>
+          <t>143170</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>178834</t>
+          <t>175262</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,02%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82629</t>
+          <t>81539</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>104549</t>
+          <t>105049</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>89477</t>
+          <t>88414</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>111719</t>
+          <t>111999</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>174682</t>
+          <t>176847</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>207381</t>
+          <t>208381</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,33%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13263</t>
+          <t>13333</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26957</t>
+          <t>27176</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13356</t>
+          <t>14035</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27289</t>
+          <t>27290</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>30298</t>
+          <t>31107</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>49644</t>
+          <t>50848</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,77%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>683</t>
+          <t>690</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5773</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>665</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>1422</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8804</t>
+          <t>8905</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4469</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4376</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>111731</t>
+          <t>111968</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>140189</t>
+          <t>139968</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>125323</t>
+          <t>125772</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>154672</t>
+          <t>154830</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>246176</t>
+          <t>245938</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>286825</t>
+          <t>285827</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>42,84%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>147848</t>
+          <t>146931</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>177700</t>
+          <t>177254</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>155550</t>
+          <t>156254</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>184939</t>
+          <t>184719</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>45,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>312933</t>
+          <t>312506</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>353106</t>
+          <t>352604</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>52,85%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20079</t>
+          <t>20154</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>36540</t>
+          <t>36468</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22996</t>
+          <t>23180</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40714</t>
+          <t>41102</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>47586</t>
+          <t>47508</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>71228</t>
+          <t>71262</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4063</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13364</t>
+          <t>13538</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>603</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>5623</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>648</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6422</t>
+          <t>6470</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse satisfecho con su vida en 2012 (tasa de respuesta: 97,81%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el adulto en 2012 (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54857</t>
+          <t>53742</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>73720</t>
+          <t>74374</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53107</t>
+          <t>52566</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72174</t>
+          <t>72640</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>113141</t>
+          <t>111396</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>141665</t>
+          <t>141155</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>45,21%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71844</t>
+          <t>70785</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92501</t>
+          <t>91636</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68088</t>
+          <t>67727</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>88846</t>
+          <t>88428</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>145407</t>
+          <t>144955</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>174332</t>
+          <t>174791</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,99%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3717</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13126</t>
+          <t>13131</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6379</t>
+          <t>6018</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16276</t>
+          <t>16215</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12338</t>
+          <t>12688</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25749</t>
+          <t>25869</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5473</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>588</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6088</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8234</t>
+          <t>8346</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3580</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7770</t>
+          <t>7175</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8586</t>
+          <t>7938</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38038</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58788</t>
+          <t>58422</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51535</t>
+          <t>52721</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72313</t>
+          <t>73587</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96850</t>
+          <t>96815</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>124589</t>
+          <t>126213</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>37,09%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83171</t>
+          <t>84831</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>105315</t>
+          <t>106663</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>81923</t>
+          <t>82548</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>103850</t>
+          <t>104640</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>172824</t>
+          <t>172243</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>203101</t>
+          <t>202302</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,45%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12014</t>
+          <t>11828</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26620</t>
+          <t>26297</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10155</t>
+          <t>9396</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21328</t>
+          <t>21359</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24766</t>
+          <t>24033</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>42981</t>
+          <t>41847</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>671</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5852</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>699</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>6709</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2298</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10141</t>
+          <t>9991</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7246</t>
+          <t>6604</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>633</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>6053</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8956</t>
+          <t>8976</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>99302</t>
+          <t>98295</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>127265</t>
+          <t>126384</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>110246</t>
+          <t>110034</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>139237</t>
+          <t>139856</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>217769</t>
+          <t>218049</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>258594</t>
+          <t>258627</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,64%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>162906</t>
+          <t>162873</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>192042</t>
+          <t>192118</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>154927</t>
+          <t>155316</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>186082</t>
+          <t>185221</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>325838</t>
+          <t>326822</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>367315</t>
+          <t>367572</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,33%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18603</t>
+          <t>18022</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34875</t>
+          <t>34540</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19191</t>
+          <t>18688</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33553</t>
+          <t>34212</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>39747</t>
+          <t>39093</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>62300</t>
+          <t>61998</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2541</t>
+          <t>2414</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11227</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>4663</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14999</t>
+          <t>15370</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>624</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7463</t>
+          <t>7651</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10296</t>
+          <t>9887</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3934</t>
+          <t>3908</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14282</t>
+          <t>14261</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse satisfecho con su vida en 2016 (tasa de respuesta: 98,62%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el adulto en 2016 (tasa de respuesta: 98,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>78758</t>
+          <t>79265</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>101036</t>
+          <t>101873</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>82722</t>
+          <t>82791</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>105805</t>
+          <t>106459</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>167714</t>
+          <t>169108</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>198635</t>
+          <t>201053</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>54,05%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72619</t>
+          <t>72099</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94698</t>
+          <t>94307</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66066</t>
+          <t>65396</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>88327</t>
+          <t>87727</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>146824</t>
+          <t>144129</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>176735</t>
+          <t>175119</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>47,08%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14831</t>
+          <t>15123</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5816</t>
+          <t>5730</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16377</t>
+          <t>16417</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13218</t>
+          <t>13167</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>26944</t>
+          <t>26895</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -5623,12 +5623,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>621</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6500</t>
+          <t>6436</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>790</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>7984</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2563</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10712</t>
+          <t>10074</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5042</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5788</t>
+          <t>5970</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55711</t>
+          <t>56949</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77977</t>
+          <t>77490</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>66521</t>
+          <t>66689</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88352</t>
+          <t>88639</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>128225</t>
+          <t>129383</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159399</t>
+          <t>159634</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,47%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71879</t>
+          <t>70234</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94822</t>
+          <t>91978</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77902</t>
+          <t>76600</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>98496</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>154116</t>
+          <t>154373</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>184806</t>
+          <t>185615</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>54,04%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12064</t>
+          <t>12268</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25756</t>
+          <t>25758</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>3525</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12546</t>
+          <t>12733</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>17652</t>
+          <t>17889</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>34403</t>
+          <t>33783</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -6305,12 +6305,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>994</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7257</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6320,12 +6320,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4647</t>
+          <t>4498</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8845</t>
+          <t>8666</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3895</t>
+          <t>4155</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>3835</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>140380</t>
+          <t>141120</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>171105</t>
+          <t>171141</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>156566</t>
+          <t>155334</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>186644</t>
+          <t>187166</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>307394</t>
+          <t>306581</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>351236</t>
+          <t>350560</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,0%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>150512</t>
+          <t>150258</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>183954</t>
+          <t>180635</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>148297</t>
+          <t>148238</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>179901</t>
+          <t>180689</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>306227</t>
+          <t>307059</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>351236</t>
+          <t>351845</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,18%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19973</t>
+          <t>19242</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35538</t>
+          <t>35710</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11400</t>
+          <t>11357</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>24947</t>
+          <t>25410</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>34252</t>
+          <t>35039</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>55827</t>
+          <t>56341</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2547</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10788</t>
+          <t>10864</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1644</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9475</t>
+          <t>9849</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5461</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16241</t>
+          <t>17110</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -7105,7 +7105,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07A05-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A05-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el adulto en 2007 (tasa de respuesta: 99,7%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el/la adulto/a [KIDSCREEN 20] en 2007 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>57277</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>48083</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>66699</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>40,47%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>33,98%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>47,13%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>48027</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>39811</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>57042</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>39023</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>56442</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>37,65%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>31,21%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>44,72%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>57277</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>49161</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>66984</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>40,47%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92481</t>
+          <t>93564</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>117428</t>
+          <t>119633</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>44,46%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>70898</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>61081</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>79912</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>50,1%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>43,16%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>56,47%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>69214</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>59364</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>77730</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>60315</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>79444</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>54,26%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>46,54%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>60,94%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>70898</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>62051</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>80467</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>50,1%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>127518</t>
+          <t>128205</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>152870</t>
+          <t>153372</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>57,0%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10794</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6375</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>16313</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7,63%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4,5%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>11,53%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>7722</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4125</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>13091</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>4257</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>12734</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>6,05%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>10,26%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>10794</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>6428</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>17001</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>7,63%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12528</t>
+          <t>12646</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25811</t>
+          <t>26387</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -1066,102 +1066,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1867</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>543</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5060</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>1980</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>631</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5310</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5256</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,55%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>4,12%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>3848</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>1328</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>7714</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,49%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1867</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>551</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>3848</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>1841</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>8342</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -1179,87 +1179,87 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3700</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>605</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3386</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2807</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,47%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3441</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1285</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4525</t>
+          <t>4514</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>82137</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>70436</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>92516</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>40,25%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>34,52%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>45,33%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>78313</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>67229</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>89512</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>68246</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>90592</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>40,35%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>34,64%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>46,12%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>82137</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>71610</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>93632</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>40,25%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>143170</t>
+          <t>144433</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>175262</t>
+          <t>176313</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>44,28%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>99987</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>89632</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>111654</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>49,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>43,92%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>54,71%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>92736</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>81539</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>105049</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>82107</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>104121</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>47,78%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>42,01%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>54,12%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>99987</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>88414</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>111999</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>49,0%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>176847</t>
+          <t>177386</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>208381</t>
+          <t>209834</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,7%</t>
         </is>
       </c>
     </row>
@@ -1635,67 +1635,67 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>19923</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>13805</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>27280</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>9,76%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6,76%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>13,37%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>19619</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>13333</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>27176</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>13421</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>26521</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>10,11%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,87%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>14,0%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>19923</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>14035</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>27290</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>9,76%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>31107</t>
+          <t>29922</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>50848</t>
+          <t>49268</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -1748,67 +1748,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5632</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>2150</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>690</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6431</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6133</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,11%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5478</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8905</t>
+          <t>8866</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -1856,107 +1856,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1279</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4479</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4497</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,66%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1279</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>3939</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1279</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>3847</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>204072</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>204072</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>204072</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>204072</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>204072</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>204072</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>139413</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>124670</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>153795</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>40,34%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>36,07%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>44,5%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>126340</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>111968</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>139968</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>112932</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>140333</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>39,28%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>34,81%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>43,52%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>139413</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>125772</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>154830</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>40,34%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>245938</t>
+          <t>246470</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>285827</t>
+          <t>286540</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,94%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>170885</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>156403</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>185674</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>49,45%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>45,26%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>53,73%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>161950</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>146931</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>177254</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>148775</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>176045</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>50,35%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>45,68%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>55,11%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>170885</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>156254</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>184719</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>49,45%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>312506</t>
+          <t>312519</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>352604</t>
+          <t>353806</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>53,03%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>30717</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>22759</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>38908</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>8,89%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>6,59%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>11,26%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>27341</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>20154</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>36468</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>20016</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>35650</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>8,5%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>6,27%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>11,34%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>30717</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>23180</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>41102</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>8,89%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>47508</t>
+          <t>47493</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>71262</t>
+          <t>71925</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -2430,67 +2430,67 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>3893</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1362</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>7845</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>4130</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1393</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>8314</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1964</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>8405</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,28%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>3893</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>7746</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>4051</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13538</t>
+          <t>13723</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -2538,72 +2538,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3391</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>1884</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5623</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5002</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,59%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>3414</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>646</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6470</t>
+          <t>6132</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>345587</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>477</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>321645</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>321645</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>321645</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>345587</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el adulto en 2012 (tasa de respuesta: 97,81%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el/la adulto/a [KIDSCREEN 20] en 2012 (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>61897</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>50921</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>71976</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>39,51%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>32,5%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>45,94%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>64271</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>53742</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>74374</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>53578</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>73592</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>41,33%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>34,56%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>47,82%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>61897</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>52566</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>72640</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>39,51%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>111396</t>
+          <t>111853</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>141155</t>
+          <t>140066</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>44,87%</t>
         </is>
       </c>
     </row>
@@ -3111,72 +3111,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>78409</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>67816</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>88695</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>50,05%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>43,28%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>56,61%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>81546</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>70785</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>91636</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>71838</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>92492</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>52,44%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>45,52%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>58,92%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>78409</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>67727</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>88428</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>50,05%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>144955</t>
+          <t>145147</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>174791</t>
+          <t>174808</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3224,72 +3224,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10657</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6682</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>16990</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4,26%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>10,84%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>7736</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4163</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>13131</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>4240</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>13982</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>4,97%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,44%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>10657</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>6018</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>16215</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>6,8%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12688</t>
+          <t>12612</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25869</t>
+          <t>26812</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,59%</t>
         </is>
       </c>
     </row>
@@ -3337,72 +3337,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2413</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5961</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1335</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4638</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4477</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,86%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2413</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5449</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1772</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8346</t>
+          <t>7581</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -3450,72 +3450,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3298</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1260</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7202</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3105</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3396</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>3298</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1287</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>7175</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7938</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>155514</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>62265</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>52375</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>72363</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>35,67%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>30,01%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>41,46%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>48416</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>38270</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>58422</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>39467</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>58651</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>29,21%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>23,09%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>35,24%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>62265</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>52721</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>73587</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>35,67%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96815</t>
+          <t>96916</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>126213</t>
+          <t>124697</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>36,64%</t>
         </is>
       </c>
     </row>
@@ -3793,72 +3793,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>92700</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>82311</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>103949</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>53,11%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>47,16%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>59,56%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>95361</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>84831</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>106663</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>83706</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>105490</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>57,53%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>51,18%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>64,35%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>92700</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>82548</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>104640</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>53,11%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>172243</t>
+          <t>173362</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>202302</t>
+          <t>202964</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,64%</t>
         </is>
       </c>
     </row>
@@ -3906,72 +3906,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>14645</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>9647</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>21425</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>8,39%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5,53%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>12,28%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>17910</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>11828</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>26297</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>12154</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>26747</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>10,8%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,14%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>15,86%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>14645</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>9396</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>21359</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>8,39%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24033</t>
+          <t>24669</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41847</t>
+          <t>42938</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -4019,72 +4019,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2962</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>712</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7059</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,04%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2194</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>671</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6005</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6642</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,32%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,62%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2962</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>699</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6709</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2320</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9991</t>
+          <t>10977</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -4132,99 +4132,99 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1968</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5989</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1881</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6604</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>6878</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1,14%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>6053</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>4,15%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>3850</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>9546</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>1,13%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>3850</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1304</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>8976</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174540</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174540</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174540</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>165763</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>165763</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>165763</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174540</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174540</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174540</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,72 +4362,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>124162</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>110453</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>137427</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>37,49%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>33,35%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>41,49%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>112687</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>98295</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>126384</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>96921</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>125766</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>35,07%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>30,6%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>39,34%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>124162</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>110034</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>139856</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>37,49%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>218049</t>
+          <t>218151</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>258627</t>
+          <t>257992</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,54%</t>
         </is>
       </c>
     </row>
@@ -4475,72 +4475,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>171109</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>154706</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>185195</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>51,66%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>46,71%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>55,91%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>176908</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>162873</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>192118</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>162847</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>192104</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>55,06%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>50,7%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>59,8%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>171109</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>155316</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>185221</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>51,66%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>326822</t>
+          <t>325681</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>367572</t>
+          <t>369009</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,55%</t>
         </is>
       </c>
     </row>
@@ -4588,72 +4588,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>25302</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>19350</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>34343</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>7,64%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>5,84%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>10,37%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>25646</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>18022</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34540</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>18517</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>34202</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>7,98%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,61%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>10,75%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>25302</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>18688</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>34212</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>7,64%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>39093</t>
+          <t>41281</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>61998</t>
+          <t>64328</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -4701,72 +4701,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>5374</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2524</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>10617</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3,21%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>3528</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1329</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>7946</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1334</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>8038</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,1%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>5374</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>2414</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>10078</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4663</t>
+          <t>5052</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15370</t>
+          <t>14798</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -4814,72 +4814,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5267</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>9942</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>2508</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>624</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>7651</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>7574</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,78%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>5267</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>9887</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3908</t>
+          <t>4387</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14261</t>
+          <t>13752</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>331214</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>331214</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>331214</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>456</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>321278</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>321278</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>321278</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>482</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>331214</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>331214</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>331214</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el adulto en 2016 (tasa de respuesta: 98,62%)</t>
+          <t>Menores según la frecuencia de sentirse satisfecho/a con su vida, percibida por el/la adulto/a [KIDSCREEN 20] en 2016 (tasa de respuesta: 98,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5279,67 +5279,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>94152</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>83124</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>104791</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>50,63%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>44,7%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>56,35%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>90559</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>79265</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>101873</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>80376</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>102120</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>48,69%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>42,62%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>54,78%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>94152</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>82791</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>106459</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>50,63%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>169108</t>
+          <t>168256</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>201053</t>
+          <t>200643</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>53,94%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>76900</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>66729</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>87182</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>41,35%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>35,88%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>46,88%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>83348</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>72099</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>94307</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>72011</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>93915</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>44,81%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>38,77%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>50,71%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>76900</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>65396</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>87727</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>41,35%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>144129</t>
+          <t>143877</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>175119</t>
+          <t>175868</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>47,28%</t>
         </is>
       </c>
     </row>
@@ -5500,72 +5500,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10358</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6371</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>16548</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>5,57%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>8,9%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>8871</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4750</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15123</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>4757</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>14463</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>4,77%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,13%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>10358</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>5730</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>16417</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>5,57%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13167</t>
+          <t>13020</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>26895</t>
+          <t>27403</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -5618,67 +5618,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>3186</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>788</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7935</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,27%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>2568</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6436</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6591</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,38%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3186</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>790</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>7984</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10074</t>
+          <t>11347</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -5726,72 +5726,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4872</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>638</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3635</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3662</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1370</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>5007</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>636</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5970</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>185967</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>185967</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>185967</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>267</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>185983</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>185983</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>185983</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>185967</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>185967</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>185967</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5956,72 +5956,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>77768</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>66950</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>88891</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>44,84%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>38,6%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>51,25%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>66259</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>56949</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>77490</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>56521</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>77823</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>38,96%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>33,49%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>45,56%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>77768</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>66689</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>88639</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>44,84%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>129383</t>
+          <t>128246</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159634</t>
+          <t>159217</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,35%</t>
         </is>
       </c>
     </row>
@@ -6069,72 +6069,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>87269</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>76230</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>98920</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>50,32%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>43,95%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>57,04%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>82263</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>70234</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>91978</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>70997</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>94079</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>48,37%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>41,3%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>54,08%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>87269</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>76600</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>99494</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>50,32%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>154373</t>
+          <t>152089</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>185615</t>
+          <t>184312</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,66%</t>
         </is>
       </c>
     </row>
@@ -6182,72 +6182,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7088</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3556</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>12952</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>4,09%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>7,47%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>17889</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>12268</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>25758</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>12256</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>25735</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>10,52%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>7,21%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>15,15%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>7088</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>3525</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>12733</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>2,03%</t>
-        </is>
-      </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>17889</t>
+          <t>17930</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>33783</t>
+          <t>34162</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -6295,72 +6295,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1306</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4562</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2885</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>994</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7886</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6855</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,7%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,64%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1306</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4498</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8666</t>
+          <t>8688</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -6408,107 +6408,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>772</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4155</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3474</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>772</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>3835</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173431</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173431</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173431</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>170068</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>170068</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>170068</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173431</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173431</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173431</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,72 +6638,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>171921</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>155628</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>188894</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>47,84%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>43,3%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>52,56%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>156817</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>141120</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>171141</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>142511</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>171334</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>44,04%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>39,63%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>48,07%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>171921</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>155334</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>187166</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>47,84%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>306581</t>
+          <t>305925</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>350560</t>
+          <t>351166</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>49,08%</t>
         </is>
       </c>
     </row>
@@ -6751,72 +6751,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>164169</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>147922</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>180723</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>45,68%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>41,16%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>50,28%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>165611</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>150258</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>180635</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>150373</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>180935</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>46,51%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>42,2%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>50,73%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>164169</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>148238</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>180689</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>45,68%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>307059</t>
+          <t>306763</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>351845</t>
+          <t>351643</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,15%</t>
         </is>
       </c>
     </row>
@@ -6864,72 +6864,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>17446</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>11890</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>25543</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4,85%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>7,11%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>26760</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>19242</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>35710</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>19361</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>36530</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>7,52%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,4%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>10,03%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>17446</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>11357</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>25410</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>4,85%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>35039</t>
+          <t>34253</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>56341</t>
+          <t>56158</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -6977,72 +6977,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4492</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1597</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>9298</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>5453</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>2577</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>10864</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2557</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>10899</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,53%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,72%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>4492</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1642</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>9849</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17110</t>
+          <t>16520</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -7095,69 +7095,69 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>1370</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4769</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>1409</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5128</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>1,44%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1370</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>4249</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>4</t>
@@ -7170,12 +7170,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>722</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>7111</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7185,12 +7185,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>359398</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>359398</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>359398</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>356050</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>356050</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>356050</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>493</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>359398</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>359398</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>359398</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
